--- a/SGC-CKN/Excel/f810fddf-30a1-4bb9-baa1-0506c8397199_CT-02_P1_99_D800_07-04-2026.xlsx
+++ b/SGC-CKN/Excel/f810fddf-30a1-4bb9-baa1-0506c8397199_CT-02_P1_99_D800_07-04-2026.xlsx
@@ -1168,7 +1168,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.59</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-1.19</v>
@@ -1177,10 +1177,10 @@
         <v>1.83</v>
       </c>
       <c r="I11" s="5">
-        <v>0.6</v>
+        <v>1.19</v>
       </c>
       <c r="J11" s="8">
-        <v>0.33</v>
+        <v>0.65</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1276,16 +1276,16 @@
         <v>-7.59</v>
       </c>
       <c r="G14" s="16">
-        <v>-10.59</v>
+        <v>-16.39</v>
       </c>
       <c r="H14" s="16">
         <v>0.58</v>
       </c>
       <c r="I14" s="16">
-        <v>3</v>
+        <v>8.8</v>
       </c>
       <c r="J14" s="12">
-        <v>5.14</v>
+        <v>15.09</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>34</v>
@@ -1308,7 +1308,7 @@
         <v>43</v>
       </c>
       <c r="F15" s="19">
-        <v>-10.59</v>
+        <v>-16.39</v>
       </c>
       <c r="G15" s="19">
         <v>-21.59</v>
@@ -1317,10 +1317,10 @@
         <v>0.58</v>
       </c>
       <c r="I15" s="19">
-        <v>11</v>
+        <v>5.2</v>
       </c>
       <c r="J15" s="12">
-        <v>18.86</v>
+        <v>8.91</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>34</v>
@@ -1416,16 +1416,16 @@
         <v>-39.2</v>
       </c>
       <c r="G18" s="29">
-        <v>-44.9</v>
+        <v>-44.4</v>
       </c>
       <c r="H18" s="29">
         <v>3.25</v>
       </c>
       <c r="I18" s="29">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="J18" s="25">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="K18" s="30" t="s">
         <v>54</v>
@@ -1580,7 +1580,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.59</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-1.19</v>
@@ -1589,10 +1589,10 @@
         <v>1.83</v>
       </c>
       <c r="H2" s="5">
-        <v>0.6</v>
+        <v>1.19</v>
       </c>
       <c r="I2" s="8">
-        <v>0.33</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1670,16 +1670,16 @@
         <v>-7.59</v>
       </c>
       <c r="F5" s="16">
-        <v>-10.59</v>
+        <v>-16.39</v>
       </c>
       <c r="G5" s="16">
         <v>0.58</v>
       </c>
       <c r="H5" s="16">
-        <v>3</v>
+        <v>8.8</v>
       </c>
       <c r="I5" s="12">
-        <v>5.14</v>
+        <v>15.09</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1696,7 +1696,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="19">
-        <v>-10.59</v>
+        <v>-16.39</v>
       </c>
       <c r="F6" s="19">
         <v>-21.59</v>
@@ -1705,10 +1705,10 @@
         <v>0.58</v>
       </c>
       <c r="H6" s="19">
-        <v>11</v>
+        <v>5.2</v>
       </c>
       <c r="I6" s="12">
-        <v>18.86</v>
+        <v>8.91</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1786,16 +1786,16 @@
         <v>-39.2</v>
       </c>
       <c r="F9" s="29">
-        <v>-44.9</v>
+        <v>-44.4</v>
       </c>
       <c r="G9" s="29">
         <v>3.25</v>
       </c>
       <c r="H9" s="29">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="I9" s="25">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1812,19 +1812,19 @@
         <v>8</v>
       </c>
       <c r="E10" s="34">
-        <v>-0.59</v>
+        <v>0</v>
       </c>
       <c r="F10" s="34">
-        <v>-44.9</v>
+        <v>-44.4</v>
       </c>
       <c r="G10" s="34">
         <v>10.92</v>
       </c>
       <c r="H10" s="34">
-        <v>44.31</v>
+        <v>44.4</v>
       </c>
       <c r="I10" s="34">
-        <v>4.06</v>
+        <v>4.07</v>
       </c>
     </row>
   </sheetData>
